--- a/data.xlsx
+++ b/data.xlsx
@@ -2835,6 +2835,7 @@
           <t>Activo</t>
         </is>
       </c>
+      <c r="I2" s="125" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="102" t="n">
